--- a/test_cases/testing.xlsx
+++ b/test_cases/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenchim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B246F8D-116A-4482-BFE7-687AB07BF51D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E79409-9975-41A0-BE44-AF78EA9E6448}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B63FC884-ADAC-4374-AE51-F0350AD76F1C}"/>
   </bookViews>
@@ -75,34 +75,34 @@
     <t>notes</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/16wD-frbrKlrWdIBJ9ThkidCHBtriZa2u/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://www.dropbox.com/scl/fi/02n0n5arrnva4fyo70nls/IMG_5839.JPG?rlkey=84l63q8i4r756na8ppw5zurov&amp;st=biilzy77&amp;e=2&amp;dl=0</t>
-  </si>
-  <si>
-    <t>https://www.dropbox.com/scl/fi/tr51m4bkunoa7k0qhoa53/IMG_5840.JPG?rlkey=r8c0r2rg48v4qrmgawuy507g2&amp;st=tj3tidxf&amp;dl=0</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1it5W6ui84ZyG5aebiwyBegPja19T_HMw/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VCq5O1gCKV3DlSXHb7tjIrNU1VuE7y6A/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1qi-DzEpVPOc2DW8y-YpWOm51DwhTA0xn/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Ea8MuMc7MfQ8pHwby6wb0Szf4pCrcjMx/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FqziWlX1Exu5b_qroIVoXQbmRoMoId53/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/16jO083T6XQ5yQZDcpQydFfR8h6c37kWj/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1eT_cN6hm2D3fBDpDW4vHMuckl-2khk0l/view?usp=sharing</t>
+    <t>https://drive.google.com/file/d/1vcGDwEN1qkXYIUDfTIY9TL3_QAbr5Ij_/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14knN7C2yZkEk5tmCAjuDQeebipEBY973/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ujek0_KH0qIvDjJC6HzptEjfeEYf6jV5/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10pZLatbRtJL_tYerT6uE8e-SHCYdnEsF/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/180Jggyz5_ipyhRSm0ubdb5YyyaB7zKsh/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14Pn_eZ_nPoGZ-DOvwjGewv1llu7Jej-Y/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iv3OYyNZ1rULqV2CmgwSey2CmrHGBlAV/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wCDfyc5zL5kuVde3xLCeveROC_J0z4yv/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1liEHvcYcwWdS5p1Ts3EU_e3tNGumr8tb/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10nClXQFl-fJfG1KUEeGIUyAsY7STy6yQ/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -532,7 +532,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -540,7 +540,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -548,7 +548,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -557,7 +557,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -565,7 +565,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -573,7 +573,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -597,7 +597,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -605,19 +605,12 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{5807FCA9-2113-4F03-9300-9DCAD302851D}"/>
-    <hyperlink ref="B9" r:id="rId2" xr:uid="{F6664707-A19B-4C76-B8D0-2058C495D8F7}"/>
-    <hyperlink ref="B2" r:id="rId3" xr:uid="{C17E835E-BE23-4699-A3A8-5C87A5A6CC7D}"/>
-    <hyperlink ref="B8" r:id="rId4" xr:uid="{15C41BC2-EA3E-4E55-BE46-E55B797C20E0}"/>
-    <hyperlink ref="B5" r:id="rId5" xr:uid="{A9127BC0-2FDC-48AD-B79F-F2B5E143455A}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{952720E3-A546-465C-9EFF-2B06EF73AF84}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{BEF1CCBE-87E5-438F-9073-283FA0974F9C}"/>
-    <hyperlink ref="B11" r:id="rId8" xr:uid="{33228C15-3CD4-4B58-A84B-9F61C076203F}"/>
+    <hyperlink ref="B10" r:id="rId1" xr:uid="{C769F723-F91F-453E-A021-53B14E9B9E14}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
